--- a/assumptions_26_slides.xlsx
+++ b/assumptions_26_slides.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29346851.32</v>
+        <v>12318638.98</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18283880.80999999</v>
+        <v>8889910.27</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>522703468.6</v>
+        <v>549125651.48</v>
       </c>
       <c r="C8" t="n">
         <v>54400000</v>
       </c>
       <c r="D8" t="n">
-        <v>577103468.5999999</v>
+        <v>603525651.48</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7368853.849999999</v>
+        <v>6695432.629999999</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>530072322.45</v>
+        <v>555821084.11</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
